--- a/output/pdf_financials_xlsx/FTEL.xlsx
+++ b/output/pdf_financials_xlsx/FTEL.xlsx
@@ -1926,13 +1926,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.872079</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.110621</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.357187</v>
       </c>
     </row>
     <row r="93">
@@ -3327,7 +3327,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -4699,7 +4703,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="n">
         <v>0.872079</v>
       </c>

--- a/output/pdf_financials_xlsx/FTEL.xlsx
+++ b/output/pdf_financials_xlsx/FTEL.xlsx
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.011117</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
         <v>-2.297968</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.963878</v>
+        <v>-1.974995</v>
       </c>
     </row>
     <row r="28">
@@ -903,7 +903,7 @@
         <v>-2.217253</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.863622</v>
+        <v>-1.874739</v>
       </c>
     </row>
     <row r="30">
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.193839</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.012602</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.21142</v>
       </c>
     </row>
     <row r="35">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.193839</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.012602</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.00245</v>
+        <v>0.21387</v>
       </c>
     </row>
     <row r="37">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.743582</v>
+        <v>0.549743</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.104864</v>
+        <v>0.092262</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.42446</v>
+        <v>0.21304</v>
       </c>
     </row>
     <row r="49">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.007566</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.007566</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2850,7 +2850,11 @@
           <t>Reclamation deposits 4</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -4191,7 +4195,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
@@ -4387,7 +4391,11 @@
           <t>Reclamation deposit 9</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>0.136212</v>
       </c>
@@ -6383,7 +6391,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E120" s="5" t="n">
         <v>-0.007566</v>
       </c>
@@ -6910,7 +6922,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -7191,7 +7203,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -7724,7 +7736,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">

--- a/output/pdf_financials_xlsx/FTEL.xlsx
+++ b/output/pdf_financials_xlsx/FTEL.xlsx
@@ -2226,10 +2226,10 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.038352</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.171074</v>
       </c>
     </row>
     <row r="112">
@@ -2600,10 +2600,10 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.038352</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.171074</v>
       </c>
     </row>
     <row r="135">
@@ -2616,10 +2616,10 @@
         <v>-2.251038</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.021337</v>
+        <v>-1.059689</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.601357</v>
+        <v>-1.772431</v>
       </c>
     </row>
   </sheetData>
@@ -5519,7 +5519,11 @@
           <t>Purchase of equipment 5</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -6143,7 +6147,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -6207,7 +6215,11 @@
           <t>Issuance of share capital pursuant to private placement</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E114" s="5" t="n">
         <v>1.5156</v>
       </c>
